--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_53_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_53_IN_Piura.xlsx
@@ -1792,7 +1792,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>42.68</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C11" s="29">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>44.88</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>11.69</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.76</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="B15" s="42">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>13.0647</v>
       </c>
       <c r="C15" s="43">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="41" t="inlineStr">
         <is>
@@ -1934,11 +1934,11 @@
       </c>
       <c r="B16" s="45">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>11.4386</v>
       </c>
       <c r="C16" s="46">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>87.55</v>
       </c>
       <c r="D16" s="44" t="inlineStr">
         <is>
@@ -1959,11 +1959,11 @@
       </c>
       <c r="B17" s="45">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>1.6261</v>
       </c>
       <c r="C17" s="46">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>12.45</v>
       </c>
       <c r="D17" s="44" t="inlineStr">
         <is>
@@ -2138,11 +2138,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>13.0662</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2261,6 +2261,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2326,6 +2327,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -2372,6 +2374,7 @@
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="8" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="108" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
@@ -2896,11 +2899,11 @@
       </c>
       <c r="B21" s="31">
         <f>SUM(B10:B20)</f>
-        <v/>
+        <v>481.17</v>
       </c>
       <c r="C21" s="23">
         <f>SUM(C10:C20)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
@@ -2910,19 +2913,19 @@
       <c r="E21" s="17" t="inlineStr"/>
       <c r="F21" s="17">
         <f>ROUND(AVERAGE(F10:F20),2)</f>
-        <v/>
+        <v>29.39</v>
       </c>
       <c r="G21" s="22">
         <f>ROUND(AVERAGE(G10:G20),4)</f>
-        <v/>
+        <v>0.5435</v>
       </c>
       <c r="H21" s="23">
         <f>ROUND(AVERAGE(H10:H20),2)</f>
-        <v/>
+        <v>73.58</v>
       </c>
       <c r="I21" s="23">
         <f>ROUND(AVERAGE(I10:I20),2)</f>
-        <v/>
+        <v>32.8</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1">
